--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486296_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486296_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.2138</v>
+        <v>1.4943</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.5296999999999999</v>
+        <v>-0.1259</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7435</v>
+        <v>1.6202</v>
       </c>
       <c r="G2" t="n">
         <v>2.4723</v>
@@ -610,13 +610,13 @@
         <v>1.9576</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.1938</v>
+        <v>-0.9133</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6044</v>
+        <v>-0.2007</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5893</v>
+        <v>-0.7126</v>
       </c>
       <c r="V2" t="n">
         <v>-0.9347</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. ALMENTA MACIAS</t>
+          <t>A. URDIAIN LABAYEN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9866</v>
+        <v>0.6365</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6463</v>
+        <v>2.5268</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3403</v>
+        <v>-1.8904</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4008</v>
+        <v>0.0616</v>
       </c>
       <c r="H3" t="n">
-        <v>0.149</v>
+        <v>-0.0914</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2518</v>
+        <v>0.153</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0382</v>
+        <v>1.6148</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>0.657</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0382</v>
+        <v>0.9578</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3626</v>
+        <v>-1.5532</v>
       </c>
       <c r="N3" t="n">
-        <v>0.149</v>
+        <v>-0.7484</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2136</v>
+        <v>-0.8048999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.2175</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.305</v>
       </c>
       <c r="S3" t="n">
-        <v>0.781</v>
+        <v>-0.4029</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6081</v>
+        <v>0.1094</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1729</v>
+        <v>-0.5122</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.1952</v>
+        <v>0.7602</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.8902</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1952</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. COMENDADOR FEMENIAS</t>
+          <t>A. ALMENTA MACIAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9114</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2126</v>
+        <v>0.311</v>
       </c>
       <c r="F4" t="n">
-        <v>1.124</v>
+        <v>0.3094</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1505</v>
+        <v>0.4008</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.5601</v>
+        <v>0.149</v>
       </c>
       <c r="I4" t="n">
-        <v>1.4096</v>
+        <v>0.2518</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.0587</v>
+        <v>0.0382</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.3592</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3005</v>
+        <v>0.0382</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0917</v>
+        <v>0.3626</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2009</v>
+        <v>0.149</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1091</v>
+        <v>0.2136</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6525</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7401</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2141</v>
+        <v>0.4149</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5432</v>
+        <v>0.2728</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.329</v>
+        <v>0.1421</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1952</v>
+        <v>-0.1952</v>
       </c>
       <c r="W4" t="n">
-        <v>0.3904</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>-0.1952</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. URDIAIN LABAYEN</t>
+          <t>A. COMENDADOR FEMENIAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6489</v>
+        <v>0.243</v>
       </c>
       <c r="E5" t="n">
-        <v>2.5701</v>
+        <v>-0.6344</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.9212</v>
+        <v>0.8774999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0616</v>
+        <v>-0.1505</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0914</v>
+        <v>-1.5601</v>
       </c>
       <c r="I5" t="n">
-        <v>0.153</v>
+        <v>1.4096</v>
       </c>
       <c r="J5" t="n">
-        <v>1.6148</v>
+        <v>-0.0587</v>
       </c>
       <c r="K5" t="n">
-        <v>0.657</v>
+        <v>-1.3592</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9578</v>
+        <v>1.3005</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.5532</v>
+        <v>-0.0917</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7484</v>
+        <v>-0.2009</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8048999999999999</v>
+        <v>0.1091</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2175</v>
+        <v>0.6525</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R5" t="n">
-        <v>1.305</v>
+        <v>1.7401</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3904</v>
+        <v>-0.4542</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1526</v>
+        <v>0.1214</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5431</v>
+        <v>-0.5756</v>
       </c>
       <c r="V5" t="n">
-        <v>0.7602</v>
+        <v>0.1952</v>
       </c>
       <c r="W5" t="n">
-        <v>1.8902</v>
+        <v>0.3904</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.13</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. DIKE EGUN</t>
+          <t>I. MASSOUD RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6112</v>
+        <v>-0.1666</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3181</v>
+        <v>-0.5651</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.9292</v>
+        <v>0.3985</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.8067</v>
+        <v>-0.5413</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3134</v>
+        <v>-1.6848</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.4933</v>
+        <v>1.1435</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1929</v>
+        <v>-0.4209</v>
       </c>
       <c r="K6" t="n">
-        <v>1.1164</v>
+        <v>-1.4354</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0765</v>
+        <v>1.0144</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.9996</v>
+        <v>-0.1204</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.4298</v>
+        <v>-0.2495</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.5698</v>
+        <v>0.1291</v>
       </c>
       <c r="P6" t="n">
-        <v>1.7401</v>
+        <v>0.87</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.8276</v>
+        <v>0.87</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5445</v>
+        <v>-0.3001</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2127</v>
+        <v>-0.1442</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7572</v>
+        <v>-0.1559</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. MASSOUD RODRÍGUEZ</t>
+          <t>G. DIKE EGUN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6629</v>
+        <v>-0.8403</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9689</v>
+        <v>0.1198</v>
       </c>
       <c r="F7" t="n">
-        <v>0.306</v>
+        <v>-0.9601</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.5413</v>
+        <v>-1.8067</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.6848</v>
+        <v>-0.3134</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1435</v>
+        <v>-1.4933</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.4209</v>
+        <v>1.1929</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.4354</v>
+        <v>1.1164</v>
       </c>
       <c r="L7" t="n">
-        <v>1.0144</v>
+        <v>0.0765</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1204</v>
+        <v>-2.9996</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2495</v>
+        <v>-1.4298</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1291</v>
+        <v>-1.5698</v>
       </c>
       <c r="P7" t="n">
-        <v>0.87</v>
+        <v>1.7401</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R7" t="n">
-        <v>0.87</v>
+        <v>2.8276</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7964</v>
+        <v>-0.7736</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.548</v>
+        <v>0.0144</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2484</v>
+        <v>-0.788</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. CHAPELA LAGE</t>
+          <t>M. FRIERSON</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9843</v>
+        <v>-2.3465</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.1537</v>
+        <v>-1.6121</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1693</v>
+        <v>-0.7343</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.705</v>
+        <v>-1.9183</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.7512</v>
+        <v>0.6508</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0462</v>
+        <v>-2.5691</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.0507</v>
+        <v>-1.4799</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.4348</v>
+        <v>0.6022</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3841</v>
+        <v>-2.0822</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6543</v>
+        <v>-0.4383</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3164</v>
+        <v>0.0486</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3379</v>
+        <v>-0.4869</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.87</v>
+        <v>1.305</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>1.305</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4093</v>
+        <v>-0.6032</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0721</v>
+        <v>-0.1322</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4814</v>
+        <v>-0.4711</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. FRIERSON</t>
+          <t>A. CHAPELA LAGE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.8735</v>
+        <v>-2.4361</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.0159</v>
+        <v>-2.4204</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8576</v>
+        <v>-0.0156</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.9183</v>
+        <v>-0.705</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6508</v>
+        <v>-0.7512</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.5691</v>
+        <v>0.0462</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.4799</v>
+        <v>-0.0507</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6022</v>
+        <v>-0.4348</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.0822</v>
+        <v>0.3841</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4383</v>
+        <v>-0.6543</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0486</v>
+        <v>-0.3164</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4869</v>
+        <v>-0.3379</v>
       </c>
       <c r="P9" t="n">
-        <v>1.305</v>
+        <v>-0.87</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R9" t="n">
         <v>1.305</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1303</v>
+        <v>-0.861</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.536</v>
+        <v>-0.1947</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5944</v>
+        <v>-0.6663</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T. HOLLOWELL</t>
+          <t>J. FELIU ESPEJO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.6611</v>
+        <v>-3.1905</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.7252</v>
+        <v>-3.3717</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0641</v>
+        <v>0.1812</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.7911</v>
+        <v>-3.1654</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.4842</v>
+        <v>-0.5381</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.3068</v>
+        <v>-2.6272</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.2387</v>
+        <v>-1.9252</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6538</v>
+        <v>0.1952</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.5849</v>
+        <v>-2.1204</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5523</v>
+        <v>-1.2401</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8304</v>
+        <v>-0.7333</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2781</v>
+        <v>-0.5068</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.2175</v>
+        <v>0.435</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R10" t="n">
-        <v>0.87</v>
+        <v>2.6101</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6525</v>
+        <v>-1.5901</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.399</v>
+        <v>-0.4014</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2536</v>
+        <v>-1.1888</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. FELIU ESPEJO</t>
+          <t>T. HOLLOWELL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.0837</v>
+        <v>-3.2573</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.1107</v>
+        <v>-3.3215</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0271</v>
+        <v>0.0641</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.1654</v>
+        <v>-2.7911</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.5381</v>
+        <v>-1.4842</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.6272</v>
+        <v>-1.3068</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.9252</v>
+        <v>-2.2387</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1952</v>
+        <v>-0.6538</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.1204</v>
+        <v>-1.5849</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.2401</v>
+        <v>-0.5523</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7333</v>
+        <v>-0.8304</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5068</v>
+        <v>0.2781</v>
       </c>
       <c r="P11" t="n">
-        <v>0.435</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R11" t="n">
-        <v>2.6101</v>
+        <v>0.87</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.4833</v>
+        <v>-0.2488</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1404</v>
+        <v>0.0048</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.3429</v>
+        <v>-0.2536</v>
       </c>
       <c r="V11" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.8806</v>
+        <v>-5.813</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.1893</v>
+        <v>-4.2759</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.6913</v>
+        <v>-1.5372</v>
       </c>
       <c r="G12" t="n">
         <v>-3.4409</v>
@@ -1390,13 +1390,13 @@
         <v>3.6976</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.0927</v>
+        <v>-2.0252</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5888</v>
+        <v>-0.6753</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.5039</v>
+        <v>-1.3498</v>
       </c>
       <c r="V12" t="n">
         <v>-1.8695</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.955</v>
+        <v>-6.8681</v>
       </c>
       <c r="E13" t="n">
-        <v>-8.001799999999999</v>
+        <v>-7.9766</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0468</v>
+        <v>1.1085</v>
       </c>
       <c r="G13" t="n">
         <v>-3.1855</v>
@@ -1468,13 +1468,13 @@
         <v>2.1751</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5069</v>
+        <v>-0.42</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1334</v>
+        <v>-0.1081</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3735</v>
+        <v>-0.3118</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-22.9516</v>
+        <v>-21.9241</v>
       </c>
       <c r="E14" t="n">
-        <v>-22.3733</v>
+        <v>-21.346</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5782</v>
+        <v>-0.5781999999999994</v>
       </c>
       <c r="G14" t="n">
         <v>-14.77</v>
@@ -1531,7 +1531,7 @@
         <v>-8.726900000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>-5.2487</v>
+        <v>-5.248699999999999</v>
       </c>
       <c r="O14" t="n">
         <v>-3.4785</v>
@@ -1546,13 +1546,13 @@
         <v>20.6631</v>
       </c>
       <c r="S14" t="n">
-        <v>-9.205</v>
+        <v>-8.1775</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.3613</v>
+        <v>-1.3338</v>
       </c>
       <c r="U14" t="n">
-        <v>-6.8438</v>
+        <v>-6.843599999999999</v>
       </c>
       <c r="V14" t="n">
         <v>-2.2392</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.7081</v>
+        <v>8.914899999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>5.3793</v>
+        <v>5.2675</v>
       </c>
       <c r="F15" t="n">
-        <v>3.3288</v>
+        <v>3.6473</v>
       </c>
       <c r="G15" t="n">
         <v>6.9986</v>
@@ -1624,13 +1624,13 @@
         <v>2.3926</v>
       </c>
       <c r="S15" t="n">
-        <v>1.7519</v>
+        <v>1.9588</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9661999999999999</v>
+        <v>0.8544</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7858000000000001</v>
+        <v>1.1043</v>
       </c>
       <c r="V15" t="n">
         <v>-1.13</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. COSIALLS BORRAS</t>
+          <t>D. SHELIST</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.8659</v>
+        <v>6.9907</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6537</v>
+        <v>3.9852</v>
       </c>
       <c r="F16" t="n">
-        <v>4.2121</v>
+        <v>3.0056</v>
       </c>
       <c r="G16" t="n">
-        <v>3.1853</v>
+        <v>3.2089</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1557</v>
+        <v>2.9348</v>
       </c>
       <c r="I16" t="n">
-        <v>2.0296</v>
+        <v>0.2741</v>
       </c>
       <c r="J16" t="n">
-        <v>1.3535</v>
+        <v>2.4226</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6451</v>
+        <v>2.9381</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7084</v>
+        <v>-0.5155999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>1.8318</v>
+        <v>0.7863</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5107</v>
+        <v>-0.0033</v>
       </c>
       <c r="O16" t="n">
-        <v>1.3212</v>
+        <v>0.7897</v>
       </c>
       <c r="P16" t="n">
+        <v>1.5225</v>
+      </c>
+      <c r="Q16" t="n">
         <v>-0.2175</v>
       </c>
-      <c r="Q16" t="n">
-        <v>-2.1751</v>
-      </c>
       <c r="R16" t="n">
-        <v>1.9576</v>
+        <v>1.7401</v>
       </c>
       <c r="S16" t="n">
-        <v>3.8981</v>
+        <v>0.9547</v>
       </c>
       <c r="T16" t="n">
-        <v>3.4753</v>
+        <v>0.6501</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4227</v>
+        <v>0.3046</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.3045</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.1745</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. SHELIST</t>
+          <t>R. COSIALLS BORRAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>6.4075</v>
+        <v>5.4773</v>
       </c>
       <c r="E17" t="n">
-        <v>3.7617</v>
+        <v>0.9774</v>
       </c>
       <c r="F17" t="n">
-        <v>2.6459</v>
+        <v>4.4999</v>
       </c>
       <c r="G17" t="n">
-        <v>3.2089</v>
+        <v>3.1853</v>
       </c>
       <c r="H17" t="n">
-        <v>2.9348</v>
+        <v>1.1557</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2741</v>
+        <v>2.0296</v>
       </c>
       <c r="J17" t="n">
-        <v>2.4226</v>
+        <v>1.3535</v>
       </c>
       <c r="K17" t="n">
-        <v>2.9381</v>
+        <v>0.6451</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5155999999999999</v>
+        <v>0.7084</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7863</v>
+        <v>1.8318</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0033</v>
+        <v>0.5107</v>
       </c>
       <c r="O17" t="n">
-        <v>0.7897</v>
+        <v>1.3212</v>
       </c>
       <c r="P17" t="n">
-        <v>1.5225</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.2175</v>
+        <v>-2.1751</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7401</v>
+        <v>1.9576</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3716</v>
+        <v>2.5094</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4266</v>
+        <v>1.799</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0551</v>
+        <v>0.7105</v>
       </c>
       <c r="V17" t="n">
-        <v>1.3045</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.1745</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.1689</v>
+        <v>5.0565</v>
       </c>
       <c r="E18" t="n">
-        <v>1.7636</v>
+        <v>2.3224</v>
       </c>
       <c r="F18" t="n">
-        <v>2.4053</v>
+        <v>2.7341</v>
       </c>
       <c r="G18" t="n">
         <v>2.6619</v>
@@ -1858,13 +1858,13 @@
         <v>2.1751</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.233</v>
+        <v>0.6546</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3749</v>
+        <v>0.1839</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1419</v>
+        <v>0.4708</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.0607</v>
+        <v>1.184</v>
       </c>
       <c r="E19" t="n">
         <v>0.8439</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2168</v>
+        <v>0.3401</v>
       </c>
       <c r="G19" t="n">
         <v>-0.3125</v>
@@ -1936,13 +1936,13 @@
         <v>0.435</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0257</v>
+        <v>0.149</v>
       </c>
       <c r="T19" t="n">
         <v>0.0925</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0668</v>
+        <v>0.0565</v>
       </c>
       <c r="V19" t="n">
         <v>1.13</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. FAURE RIBES</t>
+          <t>F. NWAOKORIE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.0431</v>
+        <v>1.0383</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8614000000000001</v>
+        <v>-1.3497</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1817</v>
+        <v>2.388</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.798</v>
+        <v>-1.6437</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0395</v>
+        <v>0.8209</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.8375</v>
+        <v>-2.4647</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3543</v>
+        <v>-2.297</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.1246</v>
+        <v>0.1277</v>
       </c>
       <c r="L20" t="n">
-        <v>0.4789</v>
+        <v>-2.4248</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1523</v>
+        <v>0.6533</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1641</v>
+        <v>0.6932</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.3164</v>
+        <v>-0.0399</v>
       </c>
       <c r="P20" t="n">
-        <v>0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.435</v>
+        <v>-0.6525</v>
       </c>
       <c r="R20" t="n">
-        <v>1.305</v>
+        <v>1.7401</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7758</v>
+        <v>0.855</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5516</v>
+        <v>0.4699</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2242</v>
+        <v>0.3851</v>
       </c>
       <c r="V20" t="n">
-        <v>0.1952</v>
+        <v>0.7395</v>
       </c>
       <c r="W20" t="n">
-        <v>0.3904</v>
+        <v>1.13</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1952</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4381</v>
+        <v>0.7798</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5759</v>
+        <v>-0.3524</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0141</v>
+        <v>1.1322</v>
       </c>
       <c r="G21" t="n">
         <v>-0.2808</v>
@@ -2092,13 +2092,13 @@
         <v>0.6525</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4589</v>
+        <v>0.8006</v>
       </c>
       <c r="T21" t="n">
-        <v>0.024</v>
+        <v>0.2476</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4349</v>
+        <v>0.5531</v>
       </c>
       <c r="V21" t="n">
         <v>1.13</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>F. NWAOKORIE</t>
+          <t>A. FAURE RIBES</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1456</v>
+        <v>0.7335</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.9085</v>
+        <v>0.5261</v>
       </c>
       <c r="F22" t="n">
-        <v>2.0541</v>
+        <v>0.2074</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.6437</v>
+        <v>-0.798</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8209</v>
+        <v>0.0395</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.4647</v>
+        <v>-0.8375</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.297</v>
+        <v>0.3543</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1277</v>
+        <v>-0.1246</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.4248</v>
+        <v>0.4789</v>
       </c>
       <c r="M22" t="n">
-        <v>0.6533</v>
+        <v>-1.1523</v>
       </c>
       <c r="N22" t="n">
-        <v>0.6932</v>
+        <v>0.1641</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.0399</v>
+        <v>-1.3164</v>
       </c>
       <c r="P22" t="n">
-        <v>1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.6525</v>
+        <v>-0.435</v>
       </c>
       <c r="R22" t="n">
-        <v>1.7401</v>
+        <v>1.305</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0377</v>
+        <v>0.4663</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.08890000000000001</v>
+        <v>0.2163</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0512</v>
+        <v>0.2499</v>
       </c>
       <c r="V22" t="n">
-        <v>0.7395</v>
+        <v>0.1952</v>
       </c>
       <c r="W22" t="n">
-        <v>1.13</v>
+        <v>0.3904</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.3904</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.7059</v>
+        <v>-0.3411</v>
       </c>
       <c r="E23" t="n">
         <v>-1.1077</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4018</v>
+        <v>0.7665</v>
       </c>
       <c r="G23" t="n">
         <v>-0.9031</v>
@@ -2248,13 +2248,13 @@
         <v>0.6525</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5224</v>
+        <v>0.8872</v>
       </c>
       <c r="T23" t="n">
         <v>0.8376</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3152</v>
+        <v>0.0496</v>
       </c>
       <c r="V23" t="n">
         <v>-0.7602</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.5136</v>
+        <v>-1.1191</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.2191</v>
+        <v>-5.6603</v>
       </c>
       <c r="F24" t="n">
-        <v>4.7055</v>
+        <v>4.5412</v>
       </c>
       <c r="G24" t="n">
         <v>0.5282</v>
@@ -2326,13 +2326,13 @@
         <v>1.9576</v>
       </c>
       <c r="S24" t="n">
-        <v>1.2431</v>
+        <v>1.6376</v>
       </c>
       <c r="T24" t="n">
-        <v>0.3581</v>
+        <v>0.9169</v>
       </c>
       <c r="U24" t="n">
-        <v>0.885</v>
+        <v>0.7207</v>
       </c>
       <c r="V24" t="n">
         <v>0.1952</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.6667</v>
+        <v>-3.4252</v>
       </c>
       <c r="E25" t="n">
         <v>-4.8741</v>
       </c>
       <c r="F25" t="n">
-        <v>1.2074</v>
+        <v>1.4489</v>
       </c>
       <c r="G25" t="n">
         <v>2.1253</v>
@@ -2404,13 +2404,13 @@
         <v>2.3926</v>
       </c>
       <c r="S25" t="n">
-        <v>0.4282</v>
+        <v>0.6696</v>
       </c>
       <c r="T25" t="n">
         <v>0.5756</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1475</v>
+        <v>0.094</v>
       </c>
       <c r="V25" t="n">
         <v>-0.5649999999999999</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>22.9517</v>
+        <v>25.2896</v>
       </c>
       <c r="E26" t="n">
-        <v>0.5782999999999996</v>
+        <v>0.5783000000000014</v>
       </c>
       <c r="F26" t="n">
-        <v>22.3735</v>
+        <v>24.7112</v>
       </c>
       <c r="G26" t="n">
         <v>14.7701</v>
@@ -2455,7 +2455,7 @@
         <v>5.737399999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>8.727</v>
+        <v>8.726999999999999</v>
       </c>
       <c r="K26" t="n">
         <v>5.2485</v>
@@ -2482,13 +2482,13 @@
         <v>17.4007</v>
       </c>
       <c r="S26" t="n">
-        <v>9.205000000000002</v>
+        <v>11.5428</v>
       </c>
       <c r="T26" t="n">
-        <v>6.8437</v>
+        <v>6.8438</v>
       </c>
       <c r="U26" t="n">
-        <v>2.3611</v>
+        <v>4.6991</v>
       </c>
       <c r="V26" t="n">
         <v>2.2392</v>
